--- a/generated/spreadsheet/outline-planning-outline.xlsx
+++ b/generated/spreadsheet/outline-planning-outline.xlsx
@@ -808,7 +808,7 @@
       <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>List of codelist references that the document covers</t>
+          <t>Planning requirement references identifying the information this document provides. A document may address more than one requirement. These references identify its coverage; they do not establish that the requirements have been satisfied.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>MAY</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       <c r="B127" s="2" t="n"/>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Officer name</t>
+          <t>Planning officer name</t>
         </is>
       </c>
       <c r="D127" s="2" t="inlineStr"/>
@@ -4834,14 +4834,14 @@
       </c>
       <c r="D135" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Capacity unit</t>
         </is>
       </c>
       <c r="E135" s="2" t="inlineStr"/>
       <c r="F135" s="2" t="inlineStr"/>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Unit used to express the total capacity of a waste management facility</t>
         </is>
       </c>
       <c r="H135" s="2" t="inlineStr">
@@ -4896,14 +4896,14 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Unit type</t>
+          <t>Throughput unit</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr"/>
       <c r="F137" s="2" t="inlineStr"/>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Unit for capacity/throughput (e.g. cubic metres, tonnes, litres)</t>
+          <t>Unit used to express the annual throughput of a waste management facility</t>
         </is>
       </c>
       <c r="H137" s="2" t="inlineStr">
@@ -5062,7 +5062,7 @@
       <c r="F142" s="2" t="inlineStr"/>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>A description of what is being proposed, including the development, works, or change of use</t>
+          <t>A description of the development, works, change of use or reserved matters for which approval is sought</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
